--- a/HPGN/ib_results_HPGN_ibbylayer.xlsx
+++ b/HPGN/ib_results_HPGN_ibbylayer.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interainc-my.sharepoint.com/personal/jwhite_intera_com/Documents/1d_csub/clay_thicknesses/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_085D6CAF17533E0F6235547658303E38A3F98738" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F2AD1AE-AD93-418F-B8B0-787BBAC3537C}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_085D6B979763500F62355476585AAEFEB8AD8638" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37175455-2159-40F3-AA5C-6A08D2D15499}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
+    <t>Layer</t>
+  </si>
+  <si>
     <t>Aquifer Unit</t>
   </si>
   <si>
@@ -38,9 +41,6 @@
   </si>
   <si>
     <t>KV (ft/day)</t>
-  </si>
-  <si>
-    <t>Layer</t>
   </si>
   <si>
     <t>Upper</t>
@@ -68,7 +68,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -106,11 +105,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -421,255 +421,248 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="12" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1.0889369297970659</v>
+      </c>
+      <c r="E2" s="2">
+        <v>3.6768334341900001E-6</v>
+      </c>
+      <c r="F2" s="2">
+        <v>4.2568590270500003E-4</v>
+      </c>
+      <c r="G2" s="2">
+        <v>3.4509442156499998E-6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="2">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D3" s="2">
+        <v>2.8517141318193442</v>
+      </c>
+      <c r="E3" s="2">
+        <v>3.6768334341900001E-6</v>
+      </c>
+      <c r="F3" s="2">
+        <v>4.2568590270500003E-4</v>
+      </c>
+      <c r="G3" s="2">
+        <v>3.4509442156499998E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="2">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="D4" s="2">
+        <v>9.1688754484165056</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3.6768334341900001E-6</v>
+      </c>
+      <c r="F4" s="2">
+        <v>4.2568590270500003E-4</v>
+      </c>
+      <c r="G4" s="2">
+        <v>3.4509442156499998E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="2">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="D5" s="2">
+        <v>18.578588484148881</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3.6768334341900001E-6</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4.2568590270500003E-4</v>
+      </c>
+      <c r="G5" s="2">
+        <v>3.4509442156499998E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="D6" s="2">
+        <v>40.188610252405432</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2.9484099822799999E-6</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5.0895315924800002E-4</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2.6895272946300002E-6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.85167941366195965</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3.39339066943E-6</v>
+      </c>
+      <c r="F7" s="2">
+        <v>7.0863258025000001E-4</v>
+      </c>
+      <c r="G7" s="2">
+        <v>6.3548935137699997E-7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="2">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1.0889369297970659</v>
-      </c>
-      <c r="E2" s="3">
-        <v>3.6768334341900001E-6</v>
-      </c>
-      <c r="F2" s="3">
-        <v>4.2568590270500003E-4</v>
-      </c>
-      <c r="G2" s="3">
-        <v>3.4509442156499998E-6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3">
-        <v>2.8517141318193442</v>
-      </c>
-      <c r="E3" s="3">
-        <v>3.6768334341900001E-6</v>
-      </c>
-      <c r="F3" s="3">
-        <v>4.2568590270500003E-4</v>
-      </c>
-      <c r="G3" s="3">
-        <v>3.4509442156499998E-6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3">
-        <v>9.1688754484165056</v>
-      </c>
-      <c r="E4" s="3">
-        <v>3.6768334341900001E-6</v>
-      </c>
-      <c r="F4" s="3">
-        <v>4.2568590270500003E-4</v>
-      </c>
-      <c r="G4" s="3">
-        <v>3.4509442156499998E-6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3">
-        <v>18.578588484148881</v>
-      </c>
-      <c r="E5" s="3">
-        <v>3.6768334341900001E-6</v>
-      </c>
-      <c r="F5" s="3">
-        <v>4.2568590270500003E-4</v>
-      </c>
-      <c r="G5" s="3">
-        <v>3.4509442156499998E-6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>2</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="D8" s="2">
+        <v>2.562161852685521</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3.39339066943E-6</v>
+      </c>
+      <c r="F8" s="2">
+        <v>7.0863258025000001E-4</v>
+      </c>
+      <c r="G8" s="2">
+        <v>6.3548935137699997E-7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="2">
         <v>8</v>
       </c>
-      <c r="C6" s="3">
-        <v>5</v>
-      </c>
-      <c r="D6" s="3">
-        <v>40.188610252405432</v>
-      </c>
-      <c r="E6" s="3">
-        <v>2.9484099822799999E-6</v>
-      </c>
-      <c r="F6" s="3">
-        <v>5.0895315924800002E-4</v>
-      </c>
-      <c r="G6" s="3">
-        <v>2.6895272946300002E-6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="D9" s="2">
+        <v>4.3107183318025308</v>
+      </c>
+      <c r="E9" s="2">
+        <v>3.39339066943E-6</v>
+      </c>
+      <c r="F9" s="2">
+        <v>7.0863258025000001E-4</v>
+      </c>
+      <c r="G9" s="2">
+        <v>6.3548935137699997E-7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="2">
         <v>9</v>
       </c>
-      <c r="C7" s="3">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0.85167941366195965</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="D10" s="2">
+        <v>6.9575240006340842</v>
+      </c>
+      <c r="E10" s="2">
         <v>3.39339066943E-6</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F10" s="2">
         <v>7.0863258025000001E-4</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G10" s="2">
         <v>6.3548935137699997E-7</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3">
-        <v>2.562161852685521</v>
-      </c>
-      <c r="E8" s="3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="2">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2">
+        <v>13.35561545990562</v>
+      </c>
+      <c r="E11" s="2">
         <v>3.39339066943E-6</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F11" s="2">
         <v>7.0863258025000001E-4</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G11" s="2">
         <v>6.3548935137699997E-7</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3">
-        <v>4.3107183318025308</v>
-      </c>
-      <c r="E9" s="3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="2">
+        <v>11</v>
+      </c>
+      <c r="D12" s="2">
+        <v>32.966013067114787</v>
+      </c>
+      <c r="E12" s="2">
         <v>3.39339066943E-6</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F12" s="2">
         <v>7.0863258025000001E-4</v>
       </c>
-      <c r="G9" s="3">
-        <v>6.3548935137699997E-7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="3">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3">
-        <v>6.9575240006340842</v>
-      </c>
-      <c r="E10" s="3">
-        <v>3.39339066943E-6</v>
-      </c>
-      <c r="F10" s="3">
-        <v>7.0863258025000001E-4</v>
-      </c>
-      <c r="G10" s="3">
-        <v>6.3548935137699997E-7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3">
-        <v>10</v>
-      </c>
-      <c r="D11" s="3">
-        <v>13.35561545990562</v>
-      </c>
-      <c r="E11" s="3">
-        <v>3.39339066943E-6</v>
-      </c>
-      <c r="F11" s="3">
-        <v>7.0863258025000001E-4</v>
-      </c>
-      <c r="G11" s="3">
-        <v>6.3548935137699997E-7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="3">
-        <v>11</v>
-      </c>
-      <c r="D12" s="3">
-        <v>32.966013067114787</v>
-      </c>
-      <c r="E12" s="3">
-        <v>3.39339066943E-6</v>
-      </c>
-      <c r="F12" s="3">
-        <v>7.0863258025000001E-4</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
         <v>6.3548935137699997E-7</v>
       </c>
     </row>
